--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run1/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run1/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="494">
   <si>
     <t>Filename</t>
   </si>
@@ -808,673 +808,694 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9879,0.0026,0.0013,0.0010</t>
-  </si>
-  <si>
-    <t>0.0003,0.0224,0.0000,0.9982</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.3942,0.0007,0.0000,0.7469</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9557,0.0122,0.0041,0.0050</t>
+  </si>
+  <si>
+    <t>0.0571,0.0212,0.0000,0.8923</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.1799,0.0015,0.0000,0.8622</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0010,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0008,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9939,0.0007,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0054,0.0006,0.9954,0.0001</t>
+  </si>
+  <si>
+    <t>0.2144,0.0013,0.8516,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.0010,0.9978,0.0004</t>
+  </si>
+  <si>
+    <t>0.9987,0.0000,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.9963,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9610,0.0007,0.0289,0.0009</t>
+  </si>
+  <si>
+    <t>0.4457,0.0053,0.5601,0.0041</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.9988,0.0002</t>
+  </si>
+  <si>
+    <t>0.0026,0.0008,0.9955,0.0003</t>
+  </si>
+  <si>
+    <t>0.0222,0.0001,0.9829,0.0003</t>
+  </si>
+  <si>
+    <t>0.0546,0.0001,0.9521,0.0011</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.9240,0.0333,0.0084,0.0003</t>
+  </si>
+  <si>
+    <t>0.8974,0.0314,0.0312,0.0015</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0015</t>
+  </si>
+  <si>
+    <t>0.0100,0.9735,0.0183,0.0003</t>
+  </si>
+  <si>
+    <t>0.9964,0.0007,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9686,0.0175,0.0043,0.0005</t>
+  </si>
+  <si>
+    <t>0.9531,0.0564,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.9985,0.0365,0.0000</t>
+  </si>
+  <si>
+    <t>0.0320,0.3981,0.1062,0.0112</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9995,0.0003</t>
+  </si>
+  <si>
+    <t>0.0019,0.0045,0.9940,0.0005</t>
+  </si>
+  <si>
+    <t>0.2809,0.0000,0.3851,0.0039</t>
+  </si>
+  <si>
+    <t>0.0001,0.0301,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9990,0.0003</t>
+  </si>
+  <si>
+    <t>0.0024,0.6838,0.0069,0.9564</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9969,0.6290,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0054,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0013,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0123,0.0112,0.9825,0.0006</t>
+  </si>
+  <si>
+    <t>0.0142,0.0025,0.9797,0.0041</t>
+  </si>
+  <si>
+    <t>0.0067,0.0009,0.9949,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0004,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0026,0.0034,0.9938,0.0038</t>
+  </si>
+  <si>
+    <t>0.9956,0.0069,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0016,0.9991,0.0016</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9694,0.9976,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0014,0.9984,0.0002</t>
+  </si>
+  <si>
+    <t>0.0051,0.0030,0.9864,0.0037</t>
+  </si>
+  <si>
+    <t>0.0000,0.9819,0.9772,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9989,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0002,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.4328,0.0033,0.5498,0.0008</t>
+  </si>
+  <si>
+    <t>0.0008,0.0004,0.9994,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9804,0.7986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.8128,0.9568,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9952,0.0339,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9962,0.6391,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0049,0.9989</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.0007,0.9999</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0001,0.9956,0.3071,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.8934,0.9832,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.9194,0.7220,0.0015</t>
+  </si>
+  <si>
+    <t>0.0001,0.9515,0.9763,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9953,0.9697,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.8960,0.9822,0.0000</t>
+  </si>
+  <si>
+    <t>0.9971,0.0041,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0013,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0022,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0010,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0018,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9968,0.0061,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0004,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9996,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0016,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0016,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9830,0.0006,0.0114,0.0002</t>
-  </si>
-  <si>
-    <t>0.0333,0.0019,0.9616,0.0039</t>
-  </si>
-  <si>
-    <t>0.4996,0.0008,0.6072,0.0003</t>
-  </si>
-  <si>
-    <t>0.0015,0.0005,0.9981,0.0002</t>
-  </si>
-  <si>
-    <t>0.9774,0.0005,0.0164,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0003,0.0000</t>
+    <t>0.0001,0.0001,0.9998,0.0008</t>
+  </si>
+  <si>
+    <t>0.0270,0.0048,0.9667,0.0012</t>
+  </si>
+  <si>
+    <t>0.9937,0.0001,0.0026,0.0001</t>
+  </si>
+  <si>
+    <t>0.0125,0.0002,0.9905,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9981,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9990,0.0020,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0800,0.9396,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9247,0.0006,0.0722,0.0011</t>
-  </si>
-  <si>
-    <t>0.2662,0.0006,0.8223,0.0005</t>
-  </si>
-  <si>
-    <t>0.0016,0.0002,0.9978,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0008,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0002,0.9984,0.0005</t>
-  </si>
-  <si>
-    <t>0.0027,0.0004,0.9962,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.6232,0.3511,0.0038,0.0002</t>
-  </si>
-  <si>
-    <t>0.9340,0.0357,0.0084,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9999,0.0041</t>
-  </si>
-  <si>
-    <t>0.0356,0.8152,0.0855,0.0008</t>
-  </si>
-  <si>
-    <t>0.9691,0.0235,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.9875,0.0059,0.0019,0.0004</t>
-  </si>
-  <si>
-    <t>0.8239,0.2854,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9940,0.3560,0.0000</t>
-  </si>
-  <si>
-    <t>0.0135,0.0187,0.9107,0.0145</t>
-  </si>
-  <si>
-    <t>0.0004,0.0010,0.9987,0.0003</t>
-  </si>
-  <si>
-    <t>0.0078,0.0022,0.9855,0.0009</t>
-  </si>
-  <si>
-    <t>0.0132,0.0001,0.8977,0.0056</t>
-  </si>
-  <si>
-    <t>0.0001,0.1141,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0020,0.9895,0.0092,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9992,0.0006</t>
-  </si>
-  <si>
-    <t>0.0023,0.2848,0.0042,0.9729</t>
-  </si>
-  <si>
-    <t>0.0001,0.9993,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9977,0.4929,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0028,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0015,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0341,0.0062,0.9516,0.0011</t>
-  </si>
-  <si>
-    <t>0.0032,0.0005,0.9955,0.0011</t>
-  </si>
-  <si>
-    <t>0.0059,0.0003,0.9962,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0014,0.9990,0.0002</t>
-  </si>
-  <si>
-    <t>0.0041,0.0043,0.9921,0.0022</t>
-  </si>
-  <si>
-    <t>0.9987,0.0018,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9973,0.0024,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.0024,0.9985,0.0008</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.8951,0.9958,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0021,0.9977,0.0009</t>
-  </si>
-  <si>
-    <t>0.0009,0.0012,0.9973,0.0035</t>
-  </si>
-  <si>
-    <t>0.0000,0.9712,0.9708,0.0000</t>
+    <t>0.0001,0.9998,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.3225,0.7570,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.8646,0.0027,0.1124,0.0011</t>
+  </si>
+  <si>
+    <t>0.1860,0.0026,0.7769,0.0046</t>
+  </si>
+  <si>
+    <t>0.7011,0.0561,0.0464,0.0054</t>
+  </si>
+  <si>
+    <t>0.5168,0.0030,0.3796,0.0118</t>
+  </si>
+  <si>
+    <t>0.0013,0.0146,0.0033,0.9755</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9942,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.9971,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.7684,0.2693,0.0037,0.0002</t>
+  </si>
+  <si>
+    <t>0.6624,0.4091,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0003,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0008,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.3559,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.8750,0.9754,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.0126,0.9968,0.0002</t>
+  </si>
+  <si>
+    <t>0.0490,0.0016,0.9518,0.0008</t>
+  </si>
+  <si>
+    <t>0.9873,0.0002,0.0083,0.0003</t>
+  </si>
+  <si>
+    <t>0.3403,0.0212,0.3675,0.0133</t>
+  </si>
+  <si>
+    <t>0.2057,0.0002,0.8567,0.0007</t>
+  </si>
+  <si>
+    <t>0.9214,0.0012,0.0743,0.0006</t>
+  </si>
+  <si>
+    <t>0.0079,0.0002,0.0001,0.9980</t>
+  </si>
+  <si>
+    <t>0.0000,0.0006,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9970,0.9777,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.1100,0.9204,0.0022,0.0014</t>
+  </si>
+  <si>
+    <t>0.0515,0.9572,0.0021,0.0010</t>
+  </si>
+  <si>
+    <t>0.1578,0.0001,0.0029,0.8616</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0079,0.9973,0.0067</t>
+  </si>
+  <si>
+    <t>0.9692,0.0001,0.0081,0.0061</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.2429,0.8289,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.7467,0.2839,0.0025,0.0009</t>
+  </si>
+  <si>
+    <t>0.9809,0.0072,0.0053,0.0008</t>
+  </si>
+  <si>
+    <t>0.9970,0.0005,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.8749,0.1061,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9698,0.0419,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9296,0.1006,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9413,0.0256,0.0144,0.0005</t>
+  </si>
+  <si>
+    <t>0.6182,0.4724,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9966,0.0024,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9680,0.0346,0.0011,0.0009</t>
+  </si>
+  <si>
+    <t>0.0000,0.0044,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9582,0.0463,0.0022,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0005,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0070,0.0533,0.9613,0.0066</t>
+  </si>
+  <si>
+    <t>0.0012,0.0002,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0024,0.9985,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.0044,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0007,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0073,0.0015,0.9900,0.0004</t>
+  </si>
+  <si>
+    <t>0.0337,0.0020,0.9680,0.0003</t>
+  </si>
+  <si>
+    <t>0.4144,0.0159,0.5020,0.0021</t>
+  </si>
+  <si>
+    <t>0.0241,0.0023,0.9763,0.0001</t>
+  </si>
+  <si>
+    <t>0.0177,0.1690,0.8365,0.0005</t>
+  </si>
+  <si>
+    <t>0.7792,0.0036,0.2638,0.0003</t>
+  </si>
+  <si>
+    <t>0.9553,0.0012,0.0290,0.0012</t>
+  </si>
+  <si>
+    <t>0.7751,0.0208,0.1127,0.0020</t>
+  </si>
+  <si>
+    <t>0.5124,0.6914,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.9976,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.6541,0.4998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9468,0.0708,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.8052,0.2534,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.7590,0.0954,0.0113,0.0016</t>
+  </si>
+  <si>
+    <t>0.9887,0.0002,0.0059,0.0003</t>
+  </si>
+  <si>
+    <t>0.9340,0.0049,0.0136,0.0041</t>
+  </si>
+  <si>
+    <t>0.9694,0.0019,0.0165,0.0003</t>
+  </si>
+  <si>
+    <t>0.1659,0.0031,0.8632,0.0008</t>
+  </si>
+  <si>
+    <t>0.0037,0.0006,0.9946,0.0021</t>
+  </si>
+  <si>
+    <t>0.0151,0.0164,0.9517,0.0028</t>
+  </si>
+  <si>
+    <t>0.0001,0.0037,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0212,0.0006,0.9750,0.0005</t>
+  </si>
+  <si>
+    <t>0.0003,0.0328,0.9975,0.0004</t>
+  </si>
+  <si>
+    <t>0.9986,0.0009,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0014,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9972,0.0029,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0013,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0009,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0008,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0034,0.0031,0.9951,0.0014</t>
+  </si>
+  <si>
+    <t>0.2414,0.3105,0.2403,0.0009</t>
+  </si>
+  <si>
+    <t>0.9768,0.0024,0.0049,0.0033</t>
+  </si>
+  <si>
+    <t>0.0137,0.0004,0.9902,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0008,0.9997,0.0003</t>
+  </si>
+  <si>
+    <t>0.0008,0.0035,0.9973,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0309,0.0006,0.9725,0.0007</t>
   </si>
   <si>
     <t>0.0000,0.0001,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0008,0.9987,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0002,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.4905,0.0030,0.4963,0.0005</t>
-  </si>
-  <si>
-    <t>0.0008,0.0004,0.9992,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9907,0.9542,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9656,0.4611,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.0299,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9965,0.8447,0.0000</t>
-  </si>
-  <si>
-    <t>0.0054,0.0001,0.0006,0.9976</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0002,0.9999</t>
-  </si>
-  <si>
-    <t>0.0015,0.0001,0.0000,0.9994</t>
-  </si>
-  <si>
-    <t>0.0001,0.9946,0.3559,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.9233,0.9324,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.9804,0.2888,0.0022</t>
-  </si>
-  <si>
-    <t>0.0002,0.7584,0.9637,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9910,0.9943,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9952,0.7796,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0022,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0010,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0014,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0552,0.0009,0.9506,0.0011</t>
-  </si>
-  <si>
-    <t>0.9550,0.0004,0.0400,0.0007</t>
-  </si>
-  <si>
-    <t>0.0017,0.0002,0.9985,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9983,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.9978,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0710,0.9279,0.0056,0.0003</t>
-  </si>
-  <si>
-    <t>0.0872,0.0036,0.9034,0.0021</t>
-  </si>
-  <si>
-    <t>0.1941,0.0008,0.8354,0.0010</t>
-  </si>
-  <si>
-    <t>0.9637,0.0037,0.0122,0.0007</t>
-  </si>
-  <si>
-    <t>0.1309,0.0225,0.7914,0.0065</t>
-  </si>
-  <si>
-    <t>0.0011,0.0924,0.0338,0.6306</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9972,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0022,0.9971,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.3127,0.7620,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.6982,0.3695,0.0027,0.0002</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9971,0.0015,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.4011,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.8704,0.9785,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0915,0.9952,0.0001</t>
-  </si>
-  <si>
-    <t>0.0040,0.0012,0.9937,0.0001</t>
-  </si>
-  <si>
-    <t>0.9929,0.0001,0.0034,0.0002</t>
-  </si>
-  <si>
-    <t>0.9238,0.0018,0.0430,0.0024</t>
-  </si>
-  <si>
-    <t>0.7825,0.0001,0.3311,0.0002</t>
-  </si>
-  <si>
-    <t>0.9016,0.0005,0.1318,0.0002</t>
-  </si>
-  <si>
-    <t>0.0016,0.0001,0.0040,0.9987</t>
-  </si>
-  <si>
-    <t>0.0004,0.0003,0.0001,0.9997</t>
-  </si>
-  <si>
-    <t>0.0000,0.9948,0.9607,0.0000</t>
-  </si>
-  <si>
-    <t>0.9898,0.0082,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.0043,0.9946,0.0006,0.0015</t>
-  </si>
-  <si>
-    <t>0.1142,0.9210,0.0011,0.0006</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0228,0.0003,0.0001,0.9901</t>
-  </si>
-  <si>
-    <t>0.0002,0.0018,0.9987,0.0056</t>
-  </si>
-  <si>
-    <t>0.9570,0.0000,0.0014,0.0230</t>
-  </si>
-  <si>
-    <t>0.0742,0.9293,0.0049,0.0004</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9882,0.0075,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9972,0.0003,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9922,0.0033,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.8554,0.1343,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9506,0.0579,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9761,0.0222,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.1181,0.3304,0.5016,0.0010</t>
-  </si>
-  <si>
-    <t>0.4347,0.6702,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9918,0.0057,0.0010,0.0008</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9814,0.0232,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0050,0.9999,0.0004</t>
-  </si>
-  <si>
-    <t>0.9611,0.0456,0.0016,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0006,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0032,0.0062,0.9913,0.0021</t>
-  </si>
-  <si>
-    <t>0.0009,0.0004,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0022,0.0206,0.9829,0.0012</t>
-  </si>
-  <si>
-    <t>0.0004,0.0023,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0008,0.9994,0.0002</t>
-  </si>
-  <si>
-    <t>0.0347,0.0109,0.9497,0.0015</t>
-  </si>
-  <si>
-    <t>0.1089,0.0135,0.8329,0.0057</t>
-  </si>
-  <si>
-    <t>0.0269,0.0110,0.9575,0.0008</t>
-  </si>
-  <si>
-    <t>0.0659,0.0125,0.8819,0.0010</t>
-  </si>
-  <si>
-    <t>0.0223,0.2150,0.7808,0.0005</t>
-  </si>
-  <si>
-    <t>0.8812,0.0056,0.1019,0.0007</t>
-  </si>
-  <si>
-    <t>0.8616,0.0011,0.0730,0.0078</t>
-  </si>
-  <si>
-    <t>0.7087,0.0054,0.2007,0.0013</t>
-  </si>
-  <si>
-    <t>0.6949,0.4616,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0040,0.9962,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.6650,0.4722,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9624,0.0490,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.6420,0.4819,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9735,0.0034,0.0053,0.0004</t>
-  </si>
-  <si>
-    <t>0.9983,0.0001,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.5113,0.0425,0.0934,0.0329</t>
-  </si>
-  <si>
-    <t>0.0601,0.0250,0.9046,0.0009</t>
-  </si>
-  <si>
-    <t>0.8533,0.0041,0.0824,0.0110</t>
-  </si>
-  <si>
-    <t>0.0024,0.0011,0.9962,0.0005</t>
-  </si>
-  <si>
-    <t>0.0432,0.0130,0.8599,0.0326</t>
-  </si>
-  <si>
-    <t>0.0011,0.0094,0.9955,0.0002</t>
-  </si>
-  <si>
-    <t>0.0335,0.0010,0.9496,0.0039</t>
-  </si>
-  <si>
-    <t>0.0026,0.0097,0.9817,0.0027</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9970,0.0024,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9985,0.0017,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0013,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0010,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0033,0.9982,0.0013</t>
-  </si>
-  <si>
-    <t>0.0147,0.2360,0.8932,0.0002</t>
-  </si>
-  <si>
-    <t>0.8246,0.0005,0.0747,0.0087</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0004,0.9993,0.0003</t>
-  </si>
-  <si>
-    <t>0.0006,0.1561,0.9872,0.0009</t>
-  </si>
-  <si>
-    <t>0.0022,0.0004,0.9970,0.0003</t>
-  </si>
-  <si>
-    <t>0.0020,0.0011,0.9954,0.0009</t>
-  </si>
-  <si>
-    <t>0.0030,0.0041,0.9895,0.0035</t>
-  </si>
-  <si>
-    <t>0.8475,0.0021,0.0888,0.0078</t>
-  </si>
-  <si>
-    <t>0.9160,0.0001,0.0949,0.0005</t>
-  </si>
-  <si>
-    <t>0.9978,0.0001,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9957,0.0053,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0011,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0664,0.0058,0.9298,0.0045</t>
-  </si>
-  <si>
-    <t>0.0015,0.0102,0.9948,0.0013</t>
-  </si>
-  <si>
-    <t>0.0006,0.0015,0.9979,0.0014</t>
-  </si>
-  <si>
-    <t>0.0035,0.0067,0.9892,0.0007</t>
-  </si>
-  <si>
-    <t>0.0003,0.0019,0.9991,0.0003</t>
-  </si>
-  <si>
-    <t>0.0100,0.0022,0.8827,0.2282</t>
-  </si>
-  <si>
-    <t>0.0109,0.0010,0.9870,0.0010</t>
-  </si>
-  <si>
-    <t>0.0020,0.0000,0.9963,0.0006</t>
-  </si>
-  <si>
-    <t>0.9892,0.0006,0.0002,0.0070</t>
-  </si>
-  <si>
-    <t>0.0006,0.0294,0.0000,0.9987</t>
-  </si>
-  <si>
-    <t>0.0020,0.0000,0.0001,0.9992</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.7817,0.0023,0.0292,0.0683</t>
+    <t>0.0007,0.0020,0.9977,0.0019</t>
+  </si>
+  <si>
+    <t>0.0056,0.0025,0.9907,0.0005</t>
+  </si>
+  <si>
+    <t>0.7651,0.0022,0.1823,0.0032</t>
+  </si>
+  <si>
+    <t>0.2692,0.0003,0.7828,0.0009</t>
+  </si>
+  <si>
+    <t>0.9806,0.0004,0.0142,0.0004</t>
+  </si>
+  <si>
+    <t>0.9992,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0014,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9972,0.0031,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9968,0.0027,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0104,0.0057,0.9807,0.0057</t>
+  </si>
+  <si>
+    <t>0.0005,0.0621,0.9963,0.0014</t>
+  </si>
+  <si>
+    <t>0.0002,0.0013,0.9993,0.0002</t>
+  </si>
+  <si>
+    <t>0.0074,0.0140,0.9763,0.0007</t>
+  </si>
+  <si>
+    <t>0.0024,0.0009,0.9939,0.0019</t>
+  </si>
+  <si>
+    <t>0.0245,0.0014,0.9639,0.0052</t>
+  </si>
+  <si>
+    <t>0.0153,0.0032,0.9750,0.0045</t>
+  </si>
+  <si>
+    <t>0.0020,0.0000,0.9970,0.0002</t>
+  </si>
+  <si>
+    <t>0.9798,0.0016,0.0002,0.0091</t>
+  </si>
+  <si>
+    <t>0.0004,0.1572,0.0000,0.9971</t>
+  </si>
+  <si>
+    <t>0.0063,0.0000,0.0003,0.9978</t>
+  </si>
+  <si>
+    <t>0.9716,0.0019,0.0103,0.0025</t>
   </si>
 </sst>
 </file>
@@ -1860,7 +1881,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1874,7 +1895,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1888,7 +1909,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1902,7 +1923,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1916,7 +1937,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1930,7 +1951,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1944,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1958,7 +1979,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1972,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1986,7 +2007,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2000,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2014,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2028,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2042,7 +2063,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2056,7 +2077,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2070,7 +2091,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2084,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2098,7 +2119,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2112,7 +2133,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2126,7 +2147,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2140,7 +2161,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2154,7 +2175,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2168,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2182,7 +2203,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2196,7 +2217,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2210,7 +2231,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2224,7 +2245,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2238,7 +2259,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2252,7 +2273,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2266,7 +2287,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2280,7 +2301,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2294,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2308,7 +2329,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2322,7 +2343,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2336,7 +2357,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2350,7 +2371,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2364,7 +2385,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2375,10 +2396,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D39" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2392,7 +2413,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2406,7 +2427,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2417,10 +2438,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2434,7 +2455,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2448,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2462,7 +2483,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2473,10 +2494,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2490,7 +2511,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2501,10 +2522,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D48" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2518,7 +2539,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2532,7 +2553,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2546,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2560,7 +2581,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2574,7 +2595,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2588,7 +2609,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2602,7 +2623,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2616,7 +2637,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2630,7 +2651,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>271</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2644,7 +2665,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2658,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2672,7 +2693,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2686,7 +2707,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2700,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>269</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2714,7 +2735,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2728,7 +2749,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2742,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2756,7 +2777,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2770,7 +2791,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2784,7 +2805,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2798,7 +2819,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2812,7 +2833,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2823,10 +2844,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2840,7 +2861,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2854,7 +2875,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2865,10 +2886,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2882,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2896,7 +2917,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2910,7 +2931,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2924,7 +2945,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2938,7 +2959,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2952,7 +2973,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2966,7 +2987,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2980,7 +3001,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2994,7 +3015,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3008,7 +3029,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3019,10 +3040,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3036,7 +3057,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3050,7 +3071,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3064,7 +3085,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3078,7 +3099,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>347</v>
+        <v>274</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3092,7 +3113,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3106,7 +3127,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3120,7 +3141,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3134,7 +3155,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3148,7 +3169,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3162,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3176,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3190,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>355</v>
+        <v>276</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3204,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3218,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>355</v>
+        <v>276</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3232,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3246,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3260,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>268</v>
+        <v>360</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3274,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3288,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3302,7 +3323,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3316,7 +3337,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3330,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3344,7 +3365,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3358,7 +3379,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3372,7 +3393,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>280</v>
+        <v>366</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3386,7 +3407,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3400,7 +3421,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3414,7 +3435,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3428,7 +3449,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3442,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3453,10 +3474,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3470,7 +3491,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3484,7 +3505,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3495,10 +3516,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3512,7 +3533,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3526,7 +3547,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3540,7 +3561,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>374</v>
+        <v>283</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3554,7 +3575,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3568,7 +3589,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3582,7 +3603,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3593,10 +3614,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3610,7 +3631,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3624,7 +3645,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3638,7 +3659,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3652,7 +3673,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>268</v>
+        <v>360</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3666,7 +3687,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3680,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>356</v>
+        <v>384</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3694,7 +3715,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3708,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3722,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3736,7 +3757,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3750,7 +3771,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3764,7 +3785,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3778,7 +3799,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3792,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3803,10 +3824,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D141" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3817,10 +3838,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3834,7 +3855,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3848,7 +3869,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3862,7 +3883,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3876,7 +3897,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>337</v>
+        <v>397</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3890,7 +3911,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3904,7 +3925,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3918,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3932,7 +3953,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3946,7 +3967,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>268</v>
+        <v>360</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3960,7 +3981,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3974,7 +3995,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>398</v>
+        <v>360</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3988,7 +4009,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4002,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>268</v>
+        <v>404</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4016,7 +4037,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4030,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4044,7 +4065,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>266</v>
+        <v>407</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4058,7 +4079,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4072,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4086,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4100,7 +4121,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4114,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4128,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4142,7 +4163,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>398</v>
+        <v>353</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4156,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>355</v>
+        <v>276</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4170,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4184,7 +4205,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4198,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>350</v>
+        <v>271</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4212,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4226,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>410</v>
+        <v>274</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4240,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4254,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4268,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4282,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4293,10 +4314,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4307,10 +4328,10 @@
         <v>259</v>
       </c>
       <c r="C177" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4324,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4338,7 +4359,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>418</v>
+        <v>271</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4352,7 +4373,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4366,7 +4387,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4380,7 +4401,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4394,7 +4415,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4408,7 +4429,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4422,7 +4443,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4436,7 +4457,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4450,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4464,7 +4485,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>427</v>
+        <v>294</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4478,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4492,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4506,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4520,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4534,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4548,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4562,7 +4583,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4576,7 +4597,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4590,7 +4611,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4601,10 +4622,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D198" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4618,7 +4639,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4632,7 +4653,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4646,7 +4667,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4660,7 +4681,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4674,7 +4695,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4688,7 +4709,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4702,7 +4723,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4713,10 +4734,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4727,10 +4748,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4744,7 +4765,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4758,7 +4779,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4772,7 +4793,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4786,7 +4807,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4800,7 +4821,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4814,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>356</v>
+        <v>325</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4828,7 +4849,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4842,7 +4863,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4856,7 +4877,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4870,7 +4891,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>352</v>
+        <v>458</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4884,7 +4905,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4898,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4912,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4926,7 +4947,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4937,10 +4958,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4954,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4968,7 +4989,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4982,7 +5003,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4996,7 +5017,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5010,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>326</v>
+        <v>468</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5024,7 +5045,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5038,7 +5059,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>326</v>
+        <v>470</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5052,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5066,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5080,7 +5101,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5091,10 +5112,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5108,7 +5129,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5122,7 +5143,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>269</v>
+        <v>476</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5136,7 +5157,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5150,7 +5171,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>471</v>
+        <v>272</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5164,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5178,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>268</v>
+        <v>479</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5192,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5206,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5220,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>409</v>
+        <v>481</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5234,7 +5255,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5248,7 +5269,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5262,7 +5283,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5276,7 +5297,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5290,7 +5311,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5304,7 +5325,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5318,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5332,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5346,7 +5367,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5360,7 +5381,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5374,7 +5395,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5388,7 +5409,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5402,7 +5423,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>485</v>
+        <v>342</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5416,7 +5437,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
